--- a/spec-tech/ig/StructureDefinition-xdm-document-entry.xlsx
+++ b/spec-tech/ig/StructureDefinition-xdm-document-entry.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-19T17:20:25+00:00</t>
+    <t>2026-07-21T08:40:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-xdm-document-entry.xlsx
+++ b/spec-tech/ig/StructureDefinition-xdm-document-entry.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-21T08:40:48+00:00</t>
+    <t>2026-07-21T15:50:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-xdm-document-entry.xlsx
+++ b/spec-tech/ig/StructureDefinition-xdm-document-entry.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-21T15:50:20+00:00</t>
+    <t>2026-07-21T16:28:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-xdm-document-entry.xlsx
+++ b/spec-tech/ig/StructureDefinition-xdm-document-entry.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-21T16:28:50+00:00</t>
+    <t>2026-07-21T16:53:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-xdm-document-entry.xlsx
+++ b/spec-tech/ig/StructureDefinition-xdm-document-entry.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-21T16:53:48+00:00</t>
+    <t>2026-07-22T08:07:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-xdm-document-entry.xlsx
+++ b/spec-tech/ig/StructureDefinition-xdm-document-entry.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T08:07:11+00:00</t>
+    <t>2026-07-22T10:39:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-xdm-document-entry.xlsx
+++ b/spec-tech/ig/StructureDefinition-xdm-document-entry.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1154" uniqueCount="187">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1154" uniqueCount="185">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T10:39:39+00:00</t>
+    <t>2026-07-22T17:16:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -295,7 +295,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Cette métadonnée représente la pertinence de la version de la fiche d'un document. </t>
+    <t>Cette métadonnée représente la pertinence de la version de la fiche d'un document.</t>
   </si>
   <si>
     <t>**Availability Status**</t>
@@ -441,9 +441,6 @@
   <si>
     <t xml:space="preserve">Identifier
 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Identifiant unique affecté au document par son créateur. </t>
   </si>
   <si>
     <t>Identifiant unique affecté au document par son créateur.</t>
@@ -501,9 +498,6 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Cette métadonnée contient les codes, libellés et codes système représentant :  -un évènement documenté (acte, traitement, diagnostic, etc…), -une modalité d'acquisition (contexte imagerie), -une région anatomique (contexte imagerie). </t>
-  </si>
-  <si>
     <t>Cette métadonnée contient les codes, libellés et codes système représentant :  -un évènement documenté (acte, traitement, diagnostic, etc…), -une modalité d'acquisition (contexte imagerie), -une région anatomique (contexte imagerie).</t>
   </si>
   <si>
@@ -522,7 +516,7 @@
     <t>xdm-document-entry.healthcareFacilityTypeCode</t>
   </si>
   <si>
-    <t xml:space="preserve">Secteur d'activité lié à la prise en charge de la personne, en lien avec le document produit. </t>
+    <t>Secteur d'activité lié à la prise en charge de la personne, en lien avec le document produit.</t>
   </si>
   <si>
     <t>Healthcare Facility Type Code**</t>
@@ -534,7 +528,7 @@
     <t>xdm-document-entry.practiceSetting</t>
   </si>
   <si>
-    <t xml:space="preserve">Contexte de l’acte qui a engendré la création du document. </t>
+    <t>Contexte de l’acte qui a engendré la création du document.</t>
   </si>
   <si>
     <t>**Practice Setting**</t>
@@ -3050,7 +3044,7 @@
         <v>138</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -3121,10 +3115,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3150,10 +3144,10 @@
         <v>91</v>
       </c>
       <c r="L22" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="M22" t="s" s="2">
         <v>141</v>
-      </c>
-      <c r="M22" t="s" s="2">
-        <v>142</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -3184,48 +3178,48 @@
       </c>
       <c r="Y22" s="2"/>
       <c r="Z22" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="AA22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF22" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="AG22" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH22" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK22" t="s" s="2">
         <v>143</v>
-      </c>
-      <c r="AA22" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB22" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC22" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD22" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE22" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF22" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="AG22" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH22" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI22" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AJ22" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AK22" t="s" s="2">
-        <v>144</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3236,7 +3230,7 @@
         <v>81</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>74</v>
@@ -3251,10 +3245,10 @@
         <v>91</v>
       </c>
       <c r="L23" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="M23" t="s" s="2">
         <v>147</v>
-      </c>
-      <c r="M23" t="s" s="2">
-        <v>148</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -3285,7 +3279,7 @@
       </c>
       <c r="Y23" s="2"/>
       <c r="Z23" t="s" s="2">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>74</v>
@@ -3303,13 +3297,13 @@
         <v>74</v>
       </c>
       <c r="AF23" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="AG23" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH23" t="s" s="2">
         <v>145</v>
-      </c>
-      <c r="AG23" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH23" t="s" s="2">
-        <v>146</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>74</v>
@@ -3323,10 +3317,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3349,13 +3343,13 @@
         <v>74</v>
       </c>
       <c r="K24" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="L24" t="s" s="2">
         <v>151</v>
       </c>
-      <c r="L24" t="s" s="2">
-        <v>152</v>
-      </c>
       <c r="M24" t="s" s="2">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -3406,7 +3400,7 @@
         <v>74</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>75</v>
@@ -3426,10 +3420,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -3455,10 +3449,10 @@
         <v>91</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -3489,7 +3483,7 @@
       </c>
       <c r="Y25" s="2"/>
       <c r="Z25" t="s" s="2">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>74</v>
@@ -3507,7 +3501,7 @@
         <v>74</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>81</v>
@@ -3527,10 +3521,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -3556,10 +3550,10 @@
         <v>91</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -3590,7 +3584,7 @@
       </c>
       <c r="Y26" s="2"/>
       <c r="Z26" t="s" s="2">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>74</v>
@@ -3608,7 +3602,7 @@
         <v>74</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>81</v>
@@ -3628,10 +3622,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -3657,10 +3651,10 @@
         <v>91</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -3691,7 +3685,7 @@
       </c>
       <c r="Y27" s="2"/>
       <c r="Z27" t="s" s="2">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>74</v>
@@ -3709,7 +3703,7 @@
         <v>74</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>81</v>
@@ -3729,10 +3723,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -3758,10 +3752,10 @@
         <v>91</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -3792,7 +3786,7 @@
       </c>
       <c r="Y28" s="2"/>
       <c r="Z28" t="s" s="2">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>74</v>
@@ -3810,7 +3804,7 @@
         <v>74</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>81</v>
@@ -3830,10 +3824,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -3859,10 +3853,10 @@
         <v>88</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -3913,7 +3907,7 @@
         <v>74</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>75</v>
@@ -3933,10 +3927,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -3962,10 +3956,10 @@
         <v>113</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -4016,7 +4010,7 @@
         <v>74</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>75</v>
@@ -4036,10 +4030,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4065,10 +4059,10 @@
         <v>116</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -4119,7 +4113,7 @@
         <v>74</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>81</v>
@@ -4139,10 +4133,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4165,13 +4159,13 @@
         <v>74</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -4222,7 +4216,7 @@
         <v>74</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>75</v>
@@ -4242,10 +4236,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -4268,13 +4262,13 @@
         <v>74</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -4325,7 +4319,7 @@
         <v>74</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>81</v>
@@ -4345,10 +4339,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -4371,13 +4365,13 @@
         <v>74</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -4428,7 +4422,7 @@
         <v>74</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>81</v>
@@ -4448,10 +4442,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -4477,10 +4471,10 @@
         <v>91</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -4511,7 +4505,7 @@
       </c>
       <c r="Y35" s="2"/>
       <c r="Z35" t="s" s="2">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>74</v>
@@ -4529,7 +4523,7 @@
         <v>74</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>81</v>

--- a/spec-tech/ig/StructureDefinition-xdm-document-entry.xlsx
+++ b/spec-tech/ig/StructureDefinition-xdm-document-entry.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T17:16:50+00:00</t>
+    <t>2026-07-23T08:53:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
